--- a/data/trans_camb/IP16_n_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 8,93</t>
+          <t>-32,04; 10,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,64; -13,92</t>
+          <t>-46,46; -11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,42; 6,11</t>
+          <t>-42,36; 7,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,51; -3,15</t>
+          <t>-41,22; -3,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 18,65</t>
+          <t>-36,98; 16,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 32,67</t>
+          <t>-22,97; 31,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 0,33</t>
+          <t>-29,03; -0,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,76; -8,73</t>
+          <t>-37,4; -8,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 12,07</t>
+          <t>-26,82; 12,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 47,64</t>
+          <t>-71,18; 65,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -32,29</t>
+          <t>-100,0; -33,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-95,54; 30,2</t>
+          <t>-98,33; 31,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,55</t>
+          <t>-96,9; -1,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,7</t>
+          <t>-100,0; 134,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 166,56</t>
+          <t>-55,23; 170,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 3,56</t>
+          <t>-74,18; 2,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,93; -25,97</t>
+          <t>-93,68; -24,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 47,82</t>
+          <t>-67,78; 45,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-35,45; -11,67</t>
+          <t>-33,38; -11,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-39,05; -18,35</t>
+          <t>-38,38; -16,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,48; -3,04</t>
+          <t>-33,02; -3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-39,19; -17,48</t>
+          <t>-37,81; -18,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,65; -15,97</t>
+          <t>-37,24; -17,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 4,19</t>
+          <t>-19,18; 3,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,48; -17,92</t>
+          <t>-33,45; -18,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,99; -19,9</t>
+          <t>-35,32; -20,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,36; -2,96</t>
+          <t>-24,35; -2,49</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,08; -31,4</t>
+          <t>-70,8; -29,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,27; -49,46</t>
+          <t>-80,23; -46,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,62; -8,11</t>
+          <t>-67,92; -8,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,8; -46,85</t>
+          <t>-79,26; -49,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,48; -43,62</t>
+          <t>-77,95; -44,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,42; 12,17</t>
+          <t>-38,64; 10,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,39; -46,64</t>
+          <t>-71,69; -47,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,78; -52,36</t>
+          <t>-76,42; -52,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,08; -7,75</t>
+          <t>-52,66; -6,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 1,6</t>
+          <t>-30,79; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 3,12</t>
+          <t>-30,47; 6,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 31,98</t>
+          <t>-10,5; 28,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -8,05</t>
+          <t>-42,86; -9,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,13; -14,17</t>
+          <t>-45,55; -14,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 7,87</t>
+          <t>-27,03; 10,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,41; -9,16</t>
+          <t>-34,23; -9,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,32; -11,89</t>
+          <t>-36,41; -10,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 11,88</t>
+          <t>-14,9; 11,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,22; 18,99</t>
+          <t>-81,32; 33,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 43,77</t>
+          <t>-81,24; 70,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 210,03</t>
+          <t>-27,11; 171,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,26; -19,95</t>
+          <t>-86,34; -28,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,85; -40,61</t>
+          <t>-94,38; -39,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 26,01</t>
+          <t>-58,48; 34,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,39; -32,43</t>
+          <t>-79,48; -32,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,35; -37,52</t>
+          <t>-83,97; -32,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 44,25</t>
+          <t>-34,12; 42,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -10,7</t>
+          <t>-29,14; -12,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -17,62</t>
+          <t>-33,92; -17,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 0,87</t>
+          <t>-22,94; 0,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,28; -18,53</t>
+          <t>-34,56; -18,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,12; -17,47</t>
+          <t>-34,27; -18,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 2,46</t>
+          <t>-15,38; 2,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,12; -17,5</t>
+          <t>-29,83; -17,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -19,9</t>
+          <t>-31,76; -19,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -1,24</t>
+          <t>-16,61; -1,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -32,2</t>
+          <t>-67,33; -34,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,25; -50,6</t>
+          <t>-79,05; -52,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 2,23</t>
+          <t>-55,0; 2,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-77,41; -50,83</t>
+          <t>-77,13; -50,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,63; -47,46</t>
+          <t>-77,25; -48,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 6,74</t>
+          <t>-35,27; 8,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,35; -48,33</t>
+          <t>-69,08; -48,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -54,84</t>
+          <t>-74,89; -55,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,04; -3,66</t>
+          <t>-39,09; -3,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16_n_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-20,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-14,94</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,58</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-11,39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-29,71</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-18,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-20,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-14,94</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>-12,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,16</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 10,3</t>
+          <t>-40,27; -0,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-46,46; -11,11</t>
+          <t>-36,47; 17,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 7,48</t>
+          <t>-20,73; 34,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,22; -3,3</t>
+          <t>-34,37; 8,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 16,86</t>
+          <t>-48,63; -13,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 31,3</t>
+          <t>-33,88; 15,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,03; -0,07</t>
+          <t>-29,35; -0,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,4; -8,39</t>
+          <t>-37,74; -7,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 12,06</t>
+          <t>-17,89; 19,39</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-67,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-48,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-34,2%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-89,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-55,35%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-67,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-48,36%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>-37,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-22,26%</t>
+          <t>-1,05%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 65,77</t>
+          <t>-91,56; 13,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,24</t>
+          <t>-100,0; 140,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,33; 31,96</t>
+          <t>-54,17; 191,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-96,9; -1,74</t>
+          <t>-72,88; 48,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,53</t>
+          <t>-100,0; -36,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 170,66</t>
+          <t>-82,48; 83,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 2,75</t>
+          <t>-74,27; 3,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,68; -24,6</t>
+          <t>-93,98; -23,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 45,55</t>
+          <t>-48,4; 76,88</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-27,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-26,96</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-7,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-23,63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-28,92</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-15,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-27,81</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-26,96</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,28</t>
+          <t>-8,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,54</t>
+          <t>-8,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-33,38; -11,21</t>
+          <t>-37,92; -17,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-38,38; -16,61</t>
+          <t>-36,93; -15,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-33,02; -3,19</t>
+          <t>-19,31; 4,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,81; -18,43</t>
+          <t>-34,52; -11,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,24; -17,06</t>
+          <t>-39,89; -19,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 3,84</t>
+          <t>-21,04; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -18,59</t>
+          <t>-33,59; -18,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,32; -20,41</t>
+          <t>-35,95; -20,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -2,49</t>
+          <t>-16,1; -0,34</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-66,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-64,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-17,8%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-55,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-68,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-37,2%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-20,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-61,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>-66,08%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-64,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-17,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-61,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-66,08%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,3%</t>
+          <t>-19,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,8; -29,64</t>
+          <t>-77,94; -44,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,23; -46,9</t>
+          <t>-78,76; -43,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,92; -8,38</t>
+          <t>-40,41; 12,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,26; -49,02</t>
+          <t>-73,14; -32,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,95; -44,19</t>
+          <t>-81,17; -51,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 10,73</t>
+          <t>-42,71; 8,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,69; -47,22</t>
+          <t>-71,89; -47,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,42; -52,93</t>
+          <t>-75,8; -53,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -6,9</t>
+          <t>-34,92; -0,36</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-25,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-30,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-9,56</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-14,9</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-13,53</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,72</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-25,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-30,85</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,98</t>
+          <t>12,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,79; 3,3</t>
+          <t>-43,22; -11,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 6,59</t>
+          <t>-46,24; -15,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 28,58</t>
+          <t>-28,27; 9,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,86; -9,93</t>
+          <t>-33,23; 1,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,55; -14,76</t>
+          <t>-31,19; 4,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 10,25</t>
+          <t>-9,28; 30,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,23; -9,72</t>
+          <t>-34,4; -9,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,41; -10,86</t>
+          <t>-35,1; -10,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 11,61</t>
+          <t>-14,88; 12,93</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-64,47%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-77,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-23,91%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-52,88%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-48,03%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-64,47%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-77,15%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,95%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-3,31%</t>
+          <t>-0,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-81,32; 33,07</t>
+          <t>-86,16; -28,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,24; 70,75</t>
+          <t>-94,79; -44,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 171,54</t>
+          <t>-56,95; 33,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-86,34; -28,99</t>
+          <t>-81,43; 17,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,38; -39,05</t>
+          <t>-83,03; 34,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 34,55</t>
+          <t>-23,36; 195,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,48; -32,69</t>
+          <t>-79,78; -32,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,97; -32,5</t>
+          <t>-83,49; -34,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 42,69</t>
+          <t>-33,93; 46,09</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-26,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-26,2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-20,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-25,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-26,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-26,2</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,1</t>
+          <t>-4,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -12,02</t>
+          <t>-34,68; -18,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -17,92</t>
+          <t>-33,84; -17,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 0,87</t>
+          <t>-14,36; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-34,56; -18,29</t>
+          <t>-28,62; -11,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -18,23</t>
+          <t>-34,7; -18,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 2,91</t>
+          <t>-12,46; 5,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,83; -17,55</t>
+          <t>-29,41; -17,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,76; -19,8</t>
+          <t>-32,15; -20,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -1,1</t>
+          <t>-11,34; 2,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-65,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-65,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-15,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-53,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-67,21%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-65,55%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-65,52%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-16,0%</t>
+          <t>-9,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,67%</t>
+          <t>-12,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -34,64</t>
+          <t>-77,01; -51,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,05; -52,49</t>
+          <t>-77,31; -49,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 2,17</t>
+          <t>-33,31; 10,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-77,13; -50,43</t>
+          <t>-66,91; -33,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,25; -48,92</t>
+          <t>-80,14; -51,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 8,13</t>
+          <t>-28,72; 16,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -48,46</t>
+          <t>-69,45; -48,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-74,89; -55,1</t>
+          <t>-75,59; -56,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,09; -3,11</t>
+          <t>-26,87; 5,98</t>
         </is>
       </c>
     </row>
